--- a/data/trans_orig/IP16A11_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A11_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>9741</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>19894</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>19088</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31922</t>
+          <t>31364</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,26%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>18528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22094</t>
+          <t>22168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24839</t>
+          <t>25397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>37673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>66,37%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21674</t>
+          <t>21615</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,06%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11493</t>
+          <t>11373</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19788</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25250</t>
+          <t>25309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36053</t>
+          <t>35812</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,32%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8830</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22039</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32302</t>
+          <t>32432</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22113</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>16857</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47765</t>
+          <t>49245</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45026</t>
+          <t>44896</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71101</t>
+          <t>71238</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33731</t>
+          <t>34892</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45220</t>
+          <t>46474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85407</t>
+          <t>83927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115156</t>
+          <t>116315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16021</t>
+          <t>16339</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16683</t>
+          <t>16322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15824</t>
+          <t>16241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28601</t>
+          <t>29294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>29794</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36971</t>
+          <t>36278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49748</t>
+          <t>49331</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,23%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>80,1%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34062</t>
+          <t>34824</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74311</t>
+          <t>72420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47792</t>
+          <t>48794</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70992</t>
+          <t>70461</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86433</t>
+          <t>88258</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133837</t>
+          <t>134394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>102713</t>
+          <t>104604</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142962</t>
+          <t>142200</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108825</t>
+          <t>109356</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132025</t>
+          <t>131023</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>223004</t>
+          <t>222447</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>270408</t>
+          <t>268583</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,27%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A11_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A11_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19894</t>
+          <t>14383</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25008</t>
+          <t>23908</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19088</t>
+          <t>17617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31364</t>
+          <t>29916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15883</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11164</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20439</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>54,09%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>14487</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10675</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18528</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>58,29%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>42,95%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>14214</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12015</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22168</t>
+          <t>18046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>31753</t>
+          <t>30097</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25397</t>
+          <t>24089</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37673</t>
+          <t>36388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>67,38%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29366</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29366</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29366</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31909</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31909</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31909</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56761</t>
+          <t>54005</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56761</t>
+          <t>54005</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56761</t>
+          <t>54005</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11306</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,6%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>49,97%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8612</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5265</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12843</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>36,75%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>54,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12119</t>
+          <t>12588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15929</t>
+          <t>15856</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21615</t>
+          <t>22199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15518</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11320</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19097</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>68,59%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>50,03%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14820</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10589</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18167</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>63,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16175</t>
+          <t>14227</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19673</t>
+          <t>17895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>30995</t>
+          <t>29746</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25309</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35812</t>
+          <t>35054</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1792</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8079</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3705</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6244</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,61%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>65,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>12659</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>51,58%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10557</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6946</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13233</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>70,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>46,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5891</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7998</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>61,39%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>83,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>16077</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>19659</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>80,1%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12346</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7786</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18169</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>18631</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6090</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32432</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>24,09%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>22671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>29703</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49245</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37398</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>31575</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>41958</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>75,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>58697</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>44896</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>71238</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>75,91%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40342</t>
+          <t>26066</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34892</t>
+          <t>20752</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46474</t>
+          <t>31281</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>99039</t>
+          <t>63465</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83927</t>
+          <t>54835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116315</t>
+          <t>70463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>77328</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>77328</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>77328</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>133172</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>133172</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>133172</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10122</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5842</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15472</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,46%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>18,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>48,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>11461</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7347</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>16339</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38,73%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55,21%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16322</t>
+          <t>16234</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>21590</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29294</t>
+          <t>28729</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22048</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16698</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>26328</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>68,54%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>51,91%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>81,84%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>18134</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13256</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>22248</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>61,27%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>44,79%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>75,18%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25198</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29794</t>
+          <t>22358</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>43332</t>
+          <t>39960</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36278</t>
+          <t>32821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49331</t>
+          <t>45921</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>74,61%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>29595</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>29595</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>29595</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>29380</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>29380</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>29380</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>61550</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>61550</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>61550</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>9698</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>13693</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>21077</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>52852</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>43130</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>64806</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>32,42%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26,45%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>39,75%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>57005</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>34824</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>72420</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>32,2%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>40,91%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48794</t>
+          <t>46517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70461</t>
+          <t>65699</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>115574</t>
+          <t>109056</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88258</t>
+          <t>95262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>134394</t>
+          <t>123271</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>110195</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>98241</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>119917</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>67,58%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>60,25%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>73,55%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>120019</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>104604</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>142200</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>67,8%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>59,09%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>80,33%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>121248</t>
+          <t>86181</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>109356</t>
+          <t>76686</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>131023</t>
+          <t>95868</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>241267</t>
+          <t>196376</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>222447</t>
+          <t>182161</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>268583</t>
+          <t>210170</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>68,81%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>163047</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>163047</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>163047</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>177024</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>177024</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>177024</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>179817</t>
+          <t>142385</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>179817</t>
+          <t>142385</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>179817</t>
+          <t>142385</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>356841</t>
+          <t>305432</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>356841</t>
+          <t>305432</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>356841</t>
+          <t>305432</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
